--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11766,6 +11766,266 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="n">
+        <v>1103.826367</v>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13T21:01:44.696Z</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13T22:31:19Z</t>
+        </is>
+      </c>
+      <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>952.405674</v>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13T21:01:44.648Z</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13T22:31:19Z</t>
+        </is>
+      </c>
+      <c r="M180" s="4" t="n"/>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>961.3855</v>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13T22:31:19Z</t>
+        </is>
+      </c>
+      <c r="M181" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="n">
+        <v>960.66</v>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13T22:31:19Z</t>
+        </is>
+      </c>
+      <c r="M182" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N182"/>
+  <dimension ref="A1:N186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12026,6 +12026,266 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>1083.905016</v>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14T21:00:59.153Z</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:16:30Z</t>
+        </is>
+      </c>
+      <c r="M183" s="4" t="n"/>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>939.333765</v>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14T21:00:59.143Z</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:16:30Z</t>
+        </is>
+      </c>
+      <c r="M184" s="4" t="n"/>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="n">
+        <v>951.395</v>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:16:30Z</t>
+        </is>
+      </c>
+      <c r="M185" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>950.8528</v>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="n"/>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:16:30Z</t>
+        </is>
+      </c>
+      <c r="M186" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N186"/>
+  <dimension ref="A1:N190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12286,6 +12286,266 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>1088.344342</v>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T21:01:41.299Z</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:22Z</t>
+        </is>
+      </c>
+      <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>943.671817</v>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T21:01:41.217Z</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:22Z</t>
+        </is>
+      </c>
+      <c r="M188" s="4" t="n"/>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>955.4404</v>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:22Z</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>956.8959</v>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K190" s="4" t="n"/>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:01:22Z</t>
+        </is>
+      </c>
+      <c r="M190" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N190"/>
+  <dimension ref="A1:N194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12546,6 +12546,266 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>1079.763023</v>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T21:01:00.985Z</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:34Z</t>
+        </is>
+      </c>
+      <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="n">
+        <v>943.331726</v>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T21:01:00.974Z</t>
+        </is>
+      </c>
+      <c r="L192" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:34Z</t>
+        </is>
+      </c>
+      <c r="M192" s="4" t="n"/>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="n">
+        <v>958.025</v>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:34Z</t>
+        </is>
+      </c>
+      <c r="M193" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="n">
+        <v>958.6048</v>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="n"/>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:07:34Z</t>
+        </is>
+      </c>
+      <c r="M194" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N194" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N194"/>
+  <dimension ref="A1:N198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12806,6 +12806,266 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="n">
+        <v>1080.899819</v>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:00:57.889Z</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:55Z</t>
+        </is>
+      </c>
+      <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="n">
+        <v>942.52951</v>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:00:57.879Z</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:55Z</t>
+        </is>
+      </c>
+      <c r="M196" s="4" t="n"/>
+      <c r="N196" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="n">
+        <v>951.498</v>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:55Z</t>
+        </is>
+      </c>
+      <c r="M197" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="n">
+        <v>952.6788</v>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17T22:57:55Z</t>
+        </is>
+      </c>
+      <c r="M198" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N198"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13066,6 +13066,266 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="n">
+        <v>1091.059498</v>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T21:01:13.038Z</t>
+        </is>
+      </c>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:37Z</t>
+        </is>
+      </c>
+      <c r="M199" s="4" t="n"/>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="n">
+        <v>950.004053</v>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T21:01:12.977Z</t>
+        </is>
+      </c>
+      <c r="L200" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:37Z</t>
+        </is>
+      </c>
+      <c r="M200" s="4" t="n"/>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="n">
+        <v>949.8655</v>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:37Z</t>
+        </is>
+      </c>
+      <c r="M201" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="n">
+        <v>951.9492</v>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K202" s="4" t="n"/>
+      <c r="L202" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:43:37Z</t>
+        </is>
+      </c>
+      <c r="M202" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:N206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13326,6 +13326,266 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="n">
+        <v>1068.34472</v>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19T21:00:59.798Z</t>
+        </is>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19T22:22:55Z</t>
+        </is>
+      </c>
+      <c r="M203" s="4" t="n"/>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="n">
+        <v>929.9705750000001</v>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19T21:00:59.788Z</t>
+        </is>
+      </c>
+      <c r="L204" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19T22:22:55Z</t>
+        </is>
+      </c>
+      <c r="M204" s="4" t="n"/>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="n">
+        <v>949.1202</v>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19T22:22:55Z</t>
+        </is>
+      </c>
+      <c r="M205" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="n">
+        <v>949.785</v>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K206" s="4" t="n"/>
+      <c r="L206" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19T22:22:55Z</t>
+        </is>
+      </c>
+      <c r="M206" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N206"/>
+  <dimension ref="A1:N210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13586,6 +13586,266 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="n">
+        <v>1074.763907</v>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20T21:01:02.289Z</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:35:28Z</t>
+        </is>
+      </c>
+      <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="n">
+        <v>935.5174950000001</v>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20T21:01:02.275Z</t>
+        </is>
+      </c>
+      <c r="L208" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:35:28Z</t>
+        </is>
+      </c>
+      <c r="M208" s="4" t="n"/>
+      <c r="N208" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="n">
+        <v>946.6241</v>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K209" s="4" t="n"/>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:35:28Z</t>
+        </is>
+      </c>
+      <c r="M209" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="n">
+        <v>948.8519</v>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K210" s="4" t="n"/>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:35:28Z</t>
+        </is>
+      </c>
+      <c r="M210" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N210" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N210"/>
+  <dimension ref="A1:N214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13846,6 +13846,266 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="n">
+        <v>1088.260953</v>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T21:01:06.047Z</t>
+        </is>
+      </c>
+      <c r="L211" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:35Z</t>
+        </is>
+      </c>
+      <c r="M211" s="4" t="n"/>
+      <c r="N211" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="n">
+        <v>949.776482</v>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T21:01:06.037Z</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:35Z</t>
+        </is>
+      </c>
+      <c r="M212" s="4" t="n"/>
+      <c r="N212" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="n">
+        <v>953.723</v>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:35Z</t>
+        </is>
+      </c>
+      <c r="M213" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="n">
+        <v>954.0324000000001</v>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="n"/>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21T23:27:35Z</t>
+        </is>
+      </c>
+      <c r="M214" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N214"/>
+  <dimension ref="A1:N218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14106,6 +14106,266 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="n">
+        <v>1090.625125</v>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T21:01:15.160Z</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:48Z</t>
+        </is>
+      </c>
+      <c r="M215" s="4" t="n"/>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="n">
+        <v>953.247803</v>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T21:01:15.121Z</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:48Z</t>
+        </is>
+      </c>
+      <c r="M216" s="4" t="n"/>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="n">
+        <v>963.9111</v>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K217" s="4" t="n"/>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:48Z</t>
+        </is>
+      </c>
+      <c r="M217" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="n">
+        <v>964.1099</v>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K218" s="4" t="n"/>
+      <c r="L218" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:07:48Z</t>
+        </is>
+      </c>
+      <c r="M218" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N218"/>
+  <dimension ref="A1:N222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14366,6 +14366,266 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="n">
+        <v>1076.040838</v>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:01:24.806Z</t>
+        </is>
+      </c>
+      <c r="L219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:22Z</t>
+        </is>
+      </c>
+      <c r="M219" s="4" t="n"/>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="n">
+        <v>945.853885</v>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T21:01:24.731Z</t>
+        </is>
+      </c>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:22Z</t>
+        </is>
+      </c>
+      <c r="M220" s="4" t="n"/>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="n">
+        <v>969.6224999999999</v>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K221" s="4" t="n"/>
+      <c r="L221" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:22Z</t>
+        </is>
+      </c>
+      <c r="M221" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N221" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="n">
+        <v>967.0203</v>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K222" s="4" t="n"/>
+      <c r="L222" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:02:22Z</t>
+        </is>
+      </c>
+      <c r="M222" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N222" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N222"/>
+  <dimension ref="A1:N226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14626,6 +14626,266 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="n">
+        <v>1088.370436</v>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T21:01:10.116Z</t>
+        </is>
+      </c>
+      <c r="L223" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:44Z</t>
+        </is>
+      </c>
+      <c r="M223" s="4" t="n"/>
+      <c r="N223" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="n">
+        <v>956.954059</v>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T21:01:10.055Z</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:44Z</t>
+        </is>
+      </c>
+      <c r="M224" s="4" t="n"/>
+      <c r="N224" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="n">
+        <v>966.5567</v>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K225" s="4" t="n"/>
+      <c r="L225" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:44Z</t>
+        </is>
+      </c>
+      <c r="M225" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N225" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="n">
+        <v>967.54</v>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K226" s="4" t="n"/>
+      <c r="L226" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:17:44Z</t>
+        </is>
+      </c>
+      <c r="M226" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N226" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N226"/>
+  <dimension ref="A1:N230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14886,6 +14886,266 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="n">
+        <v>1086.496635</v>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T21:01:11.843Z</t>
+        </is>
+      </c>
+      <c r="L227" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:25Z</t>
+        </is>
+      </c>
+      <c r="M227" s="4" t="n"/>
+      <c r="N227" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="n">
+        <v>954.3330110000001</v>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T21:01:11.789Z</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:25Z</t>
+        </is>
+      </c>
+      <c r="M228" s="4" t="n"/>
+      <c r="N228" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="n">
+        <v>972.3063</v>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K229" s="4" t="n"/>
+      <c r="L229" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:25Z</t>
+        </is>
+      </c>
+      <c r="M229" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N229" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="n">
+        <v>968.5166</v>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K230" s="4" t="n"/>
+      <c r="L230" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:23:25Z</t>
+        </is>
+      </c>
+      <c r="M230" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N230" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N230"/>
+  <dimension ref="A1:N234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15146,6 +15146,266 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="n">
+        <v>1090.151094</v>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26T21:01:06.718Z</t>
+        </is>
+      </c>
+      <c r="L231" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:03:33Z</t>
+        </is>
+      </c>
+      <c r="M231" s="4" t="n"/>
+      <c r="N231" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="n">
+        <v>958.333294</v>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26T21:01:06.708Z</t>
+        </is>
+      </c>
+      <c r="L232" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:03:33Z</t>
+        </is>
+      </c>
+      <c r="M232" s="4" t="n"/>
+      <c r="N232" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="n">
+        <v>964.7672</v>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K233" s="4" t="n"/>
+      <c r="L233" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:03:33Z</t>
+        </is>
+      </c>
+      <c r="M233" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N233" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="n">
+        <v>965.8699</v>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K234" s="4" t="n"/>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:03:33Z</t>
+        </is>
+      </c>
+      <c r="M234" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N234" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N234"/>
+  <dimension ref="A1:N238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15406,6 +15406,266 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="n">
+        <v>1083.284029</v>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27T21:01:17.562Z</t>
+        </is>
+      </c>
+      <c r="L235" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27T23:12:51Z</t>
+        </is>
+      </c>
+      <c r="M235" s="4" t="n"/>
+      <c r="N235" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="n">
+        <v>952.1005</v>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27T21:01:17.487Z</t>
+        </is>
+      </c>
+      <c r="L236" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27T23:12:51Z</t>
+        </is>
+      </c>
+      <c r="M236" s="4" t="n"/>
+      <c r="N236" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="n">
+        <v>966.0650000000001</v>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K237" s="4" t="n"/>
+      <c r="L237" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27T23:12:51Z</t>
+        </is>
+      </c>
+      <c r="M237" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N237" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="n">
+        <v>966.4237000000001</v>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K238" s="4" t="n"/>
+      <c r="L238" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27T23:12:51Z</t>
+        </is>
+      </c>
+      <c r="M238" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N238" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N238"/>
+  <dimension ref="A1:N242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15666,6 +15666,266 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="n">
+        <v>1094.719627</v>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28T21:01:14.359Z</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:07Z</t>
+        </is>
+      </c>
+      <c r="M239" s="4" t="n"/>
+      <c r="N239" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="n">
+        <v>963.988209</v>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28T21:01:14.333Z</t>
+        </is>
+      </c>
+      <c r="L240" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:07Z</t>
+        </is>
+      </c>
+      <c r="M240" s="4" t="n"/>
+      <c r="N240" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="n">
+        <v>962.8425999999999</v>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K241" s="4" t="n"/>
+      <c r="L241" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:07Z</t>
+        </is>
+      </c>
+      <c r="M241" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N241" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="n">
+        <v>964.7836</v>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K242" s="4" t="n"/>
+      <c r="L242" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:28:07Z</t>
+        </is>
+      </c>
+      <c r="M242" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N242" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -15683,7 +15683,7 @@
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>1094.719627</v>
+        <v>1086.555819</v>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
@@ -15717,12 +15717,12 @@
       </c>
       <c r="K239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28T21:01:14.359Z</t>
+          <t>2026-09-29T21:01:15.608Z</t>
         </is>
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:07Z</t>
+          <t>2026-09-29T23:51:41Z</t>
         </is>
       </c>
       <c r="M239" s="4" t="n"/>
@@ -15749,7 +15749,7 @@
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>963.988209</v>
+        <v>958.580188</v>
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
@@ -15783,12 +15783,12 @@
       </c>
       <c r="K240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28T21:01:14.333Z</t>
+          <t>2026-09-29T21:01:15.541Z</t>
         </is>
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:07Z</t>
+          <t>2026-09-29T23:51:41Z</t>
         </is>
       </c>
       <c r="M240" s="4" t="n"/>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="D241" s="5" t="n">
-        <v>962.8425999999999</v>
+        <v>959.0538</v>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:07Z</t>
+          <t>2026-09-29T23:51:41Z</t>
         </is>
       </c>
       <c r="M241" s="6" t="n">
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>964.7836</v>
+        <v>960.071</v>
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:07Z</t>
+          <t>2026-09-29T23:51:41Z</t>
         </is>
       </c>
       <c r="M242" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N242"/>
+  <dimension ref="A1:N246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15926,6 +15926,266 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="n">
+        <v>1081.208436</v>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30T21:01:20.214Z</t>
+        </is>
+      </c>
+      <c r="L243" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:02:03Z</t>
+        </is>
+      </c>
+      <c r="M243" s="4" t="n"/>
+      <c r="N243" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="n">
+        <v>954.5535170000001</v>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30T21:01:20.140Z</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:02:03Z</t>
+        </is>
+      </c>
+      <c r="M244" s="4" t="n"/>
+      <c r="N244" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="n">
+        <v>953.7558</v>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="n"/>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:02:03Z</t>
+        </is>
+      </c>
+      <c r="M245" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N245" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="n">
+        <v>953.1671</v>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K246" s="4" t="n"/>
+      <c r="L246" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:02:03Z</t>
+        </is>
+      </c>
+      <c r="M246" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N246" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N246"/>
+  <dimension ref="A1:N250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16186,6 +16186,266 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="n">
+        <v>1076.406819</v>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J247" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T21:01:13.683Z</t>
+        </is>
+      </c>
+      <c r="L247" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:09Z</t>
+        </is>
+      </c>
+      <c r="M247" s="4" t="n"/>
+      <c r="N247" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="n">
+        <v>957.66623</v>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01T21:01:13.672Z</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:09Z</t>
+        </is>
+      </c>
+      <c r="M248" s="4" t="n"/>
+      <c r="N248" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="n">
+        <v>962.4442</v>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J249" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K249" s="4" t="n"/>
+      <c r="L249" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:09Z</t>
+        </is>
+      </c>
+      <c r="M249" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N249" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="n">
+        <v>964.0522999999999</v>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J250" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K250" s="4" t="n"/>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:09Z</t>
+        </is>
+      </c>
+      <c r="M250" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N250" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="D247" s="5" t="n">
-        <v>1076.406819</v>
+        <v>1088.157574</v>
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
@@ -16237,12 +16237,12 @@
       </c>
       <c r="K247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T21:01:13.683Z</t>
+          <t>2026-10-02T21:01:17.672Z</t>
         </is>
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:09Z</t>
+          <t>2026-10-02T23:55:18Z</t>
         </is>
       </c>
       <c r="M247" s="4" t="n"/>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="D248" s="5" t="n">
-        <v>957.66623</v>
+        <v>968.038036</v>
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
@@ -16303,12 +16303,12 @@
       </c>
       <c r="K248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T21:01:13.672Z</t>
+          <t>2026-10-02T21:01:17.598Z</t>
         </is>
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:09Z</t>
+          <t>2026-10-02T23:55:18Z</t>
         </is>
       </c>
       <c r="M248" s="4" t="n"/>
@@ -16335,7 +16335,7 @@
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>962.4442</v>
+        <v>973.0646</v>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
       <c r="K249" s="4" t="n"/>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:09Z</t>
+          <t>2026-10-02T23:55:18Z</t>
         </is>
       </c>
       <c r="M249" s="6" t="n">
@@ -16399,7 +16399,7 @@
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>964.0522999999999</v>
+        <v>973.2042</v>
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
       <c r="K250" s="4" t="n"/>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:09Z</t>
+          <t>2026-10-02T23:55:18Z</t>
         </is>
       </c>
       <c r="M250" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N250"/>
+  <dimension ref="A1:N254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16446,6 +16446,266 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="n">
+        <v>1095.164601</v>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03T21:01:09.123Z</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03T23:13:58Z</t>
+        </is>
+      </c>
+      <c r="M251" s="4" t="n"/>
+      <c r="N251" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="n">
+        <v>974.827915</v>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03T21:01:09.061Z</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03T23:13:58Z</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="n"/>
+      <c r="N252" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>976.7085</v>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J253" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K253" s="4" t="n"/>
+      <c r="L253" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03T23:13:58Z</t>
+        </is>
+      </c>
+      <c r="M253" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N253" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v>976.7407000000001</v>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J254" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K254" s="4" t="n"/>
+      <c r="L254" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03T23:13:58Z</t>
+        </is>
+      </c>
+      <c r="M254" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N254" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N254"/>
+  <dimension ref="A1:N258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16706,6 +16706,266 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v>1092.180496</v>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J255" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T21:01:05.551Z</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:25:04Z</t>
+        </is>
+      </c>
+      <c r="M255" s="4" t="n"/>
+      <c r="N255" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v>971.453048</v>
+      </c>
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J256" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T21:01:05.512Z</t>
+        </is>
+      </c>
+      <c r="L256" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:25:04Z</t>
+        </is>
+      </c>
+      <c r="M256" s="4" t="n"/>
+      <c r="N256" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v>973.5236</v>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J257" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K257" s="4" t="n"/>
+      <c r="L257" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:25:04Z</t>
+        </is>
+      </c>
+      <c r="M257" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N257" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v>973.2797</v>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J258" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K258" s="4" t="n"/>
+      <c r="L258" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:25:04Z</t>
+        </is>
+      </c>
+      <c r="M258" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N258" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N258"/>
+  <dimension ref="A1:N262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16966,6 +16966,266 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v>1100.522292</v>
+      </c>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J259" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05T21:11:28.843Z</t>
+        </is>
+      </c>
+      <c r="L259" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:22:04Z</t>
+        </is>
+      </c>
+      <c r="M259" s="4" t="n"/>
+      <c r="N259" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="n">
+        <v>981.709905</v>
+      </c>
+      <c r="E260" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J260" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05T21:11:28.810Z</t>
+        </is>
+      </c>
+      <c r="L260" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:22:04Z</t>
+        </is>
+      </c>
+      <c r="M260" s="4" t="n"/>
+      <c r="N260" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="n">
+        <v>986.2578</v>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J261" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K261" s="4" t="n"/>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:22:04Z</t>
+        </is>
+      </c>
+      <c r="M261" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N261" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="n">
+        <v>986.1251</v>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J262" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K262" s="4" t="n"/>
+      <c r="L262" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T01:22:04Z</t>
+        </is>
+      </c>
+      <c r="M262" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N262" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -16983,7 +16983,7 @@
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>1100.522292</v>
+        <v>1115.971406</v>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
@@ -17017,12 +17017,12 @@
       </c>
       <c r="K259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T21:11:28.843Z</t>
+          <t>2026-10-06T21:01:04.449Z</t>
         </is>
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:04Z</t>
+          <t>2026-10-06T23:56:45Z</t>
         </is>
       </c>
       <c r="M259" s="4" t="n"/>
@@ -17049,7 +17049,7 @@
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>981.709905</v>
+        <v>991.992563</v>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="K260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T21:11:28.810Z</t>
+          <t>2026-10-06T21:01:04.438Z</t>
         </is>
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:04Z</t>
+          <t>2026-10-06T23:56:45Z</t>
         </is>
       </c>
       <c r="M260" s="4" t="n"/>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>986.2578</v>
+        <v>996.2101</v>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
       <c r="K261" s="4" t="n"/>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:04Z</t>
+          <t>2026-10-06T23:56:45Z</t>
         </is>
       </c>
       <c r="M261" s="6" t="n">
@@ -17179,7 +17179,7 @@
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>986.1251</v>
+        <v>996.5758000000001</v>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
       <c r="K262" s="4" t="n"/>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:04Z</t>
+          <t>2026-10-06T23:56:45Z</t>
         </is>
       </c>
       <c r="M262" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N262"/>
+  <dimension ref="A1:N266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17226,6 +17226,266 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="n">
+        <v>1128.026526</v>
+      </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J263" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07T19:01:07.342Z</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:18:00Z</t>
+        </is>
+      </c>
+      <c r="M263" s="4" t="n"/>
+      <c r="N263" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="n">
+        <v>1007.740545</v>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07T19:01:07.305Z</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:18:00Z</t>
+        </is>
+      </c>
+      <c r="M264" s="4" t="n"/>
+      <c r="N264" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="n">
+        <v>1015.8551</v>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="n"/>
+      <c r="L265" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:18:00Z</t>
+        </is>
+      </c>
+      <c r="M265" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N265" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="n">
+        <v>1015.0619</v>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K266" s="4" t="n"/>
+      <c r="L266" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:18:00Z</t>
+        </is>
+      </c>
+      <c r="M266" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N266" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N266"/>
+  <dimension ref="A1:N270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17486,6 +17486,266 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="n">
+        <v>1135.151222</v>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J267" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:01:17.553Z</t>
+        </is>
+      </c>
+      <c r="L267" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:51Z</t>
+        </is>
+      </c>
+      <c r="M267" s="4" t="n"/>
+      <c r="N267" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="n">
+        <v>1013.970424</v>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J268" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:01:17.494Z</t>
+        </is>
+      </c>
+      <c r="L268" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:51Z</t>
+        </is>
+      </c>
+      <c r="M268" s="4" t="n"/>
+      <c r="N268" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v>1016.7351</v>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J269" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K269" s="4" t="n"/>
+      <c r="L269" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:51Z</t>
+        </is>
+      </c>
+      <c r="M269" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N269" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="n">
+        <v>1016.9149</v>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K270" s="4" t="n"/>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:31:51Z</t>
+        </is>
+      </c>
+      <c r="M270" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N270" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N270"/>
+  <dimension ref="A1:N274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17746,6 +17746,266 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v>1129.782815</v>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T21:02:35.018Z</t>
+        </is>
+      </c>
+      <c r="L271" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:13Z</t>
+        </is>
+      </c>
+      <c r="M271" s="4" t="n"/>
+      <c r="N271" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="n">
+        <v>1009.54116</v>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T21:02:34.976Z</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:13Z</t>
+        </is>
+      </c>
+      <c r="M272" s="4" t="n"/>
+      <c r="N272" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v>1014.8033</v>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K273" s="4" t="n"/>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:13Z</t>
+        </is>
+      </c>
+      <c r="M273" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N273" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="n">
+        <v>1014.7487</v>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K274" s="4" t="n"/>
+      <c r="L274" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:11:13Z</t>
+        </is>
+      </c>
+      <c r="M274" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N274" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -17763,7 +17763,7 @@
         </is>
       </c>
       <c r="D271" s="5" t="n">
-        <v>1129.782815</v>
+        <v>1131.265267</v>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
@@ -17797,12 +17797,12 @@
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T21:02:35.018Z</t>
+          <t>2026-10-10T21:01:02.114Z</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:13Z</t>
+          <t>2026-10-10T23:42:11Z</t>
         </is>
       </c>
       <c r="M271" s="4" t="n"/>
@@ -17829,7 +17829,7 @@
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>1009.54116</v>
+        <v>1010.856786</v>
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
@@ -17863,12 +17863,12 @@
       </c>
       <c r="K272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T21:02:34.976Z</t>
+          <t>2026-10-10T21:01:02.103Z</t>
         </is>
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:13Z</t>
+          <t>2026-10-10T23:42:11Z</t>
         </is>
       </c>
       <c r="M272" s="4" t="n"/>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>1014.8033</v>
+        <v>1019.353</v>
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
       <c r="K273" s="4" t="n"/>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:13Z</t>
+          <t>2026-10-10T23:42:11Z</t>
         </is>
       </c>
       <c r="M273" s="6" t="n">
@@ -17959,7 +17959,7 @@
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>1014.7487</v>
+        <v>1013.6499</v>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
       <c r="K274" s="4" t="n"/>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:13Z</t>
+          <t>2026-10-10T23:42:11Z</t>
         </is>
       </c>
       <c r="M274" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N274"/>
+  <dimension ref="A1:N278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18006,6 +18006,266 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>1130.918499</v>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T21:01:09.295Z</t>
+        </is>
+      </c>
+      <c r="L275" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T23:48:58Z</t>
+        </is>
+      </c>
+      <c r="M275" s="4" t="n"/>
+      <c r="N275" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>1010.001824</v>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T21:01:09.235Z</t>
+        </is>
+      </c>
+      <c r="L276" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T23:48:58Z</t>
+        </is>
+      </c>
+      <c r="M276" s="4" t="n"/>
+      <c r="N276" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>1016.2436</v>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K277" s="4" t="n"/>
+      <c r="L277" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T23:48:58Z</t>
+        </is>
+      </c>
+      <c r="M277" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N277" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>1013.5293</v>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K278" s="4" t="n"/>
+      <c r="L278" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T23:48:58Z</t>
+        </is>
+      </c>
+      <c r="M278" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N278" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N278"/>
+  <dimension ref="A1:N282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18266,6 +18266,266 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>1123.723684</v>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:01:04.392Z</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:10:11Z</t>
+        </is>
+      </c>
+      <c r="M279" s="4" t="n"/>
+      <c r="N279" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>1007.664378</v>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12T21:01:04.382Z</t>
+        </is>
+      </c>
+      <c r="L280" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:10:11Z</t>
+        </is>
+      </c>
+      <c r="M280" s="4" t="n"/>
+      <c r="N280" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>1012.4591</v>
+      </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K281" s="4" t="n"/>
+      <c r="L281" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:10:11Z</t>
+        </is>
+      </c>
+      <c r="M281" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N281" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="n">
+        <v>1012.035</v>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J282" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K282" s="4" t="n"/>
+      <c r="L282" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13T02:10:11Z</t>
+        </is>
+      </c>
+      <c r="M282" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N282" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="D279" s="5" t="n">
-        <v>1123.723684</v>
+        <v>1129.71986</v>
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
@@ -18317,12 +18317,12 @@
       </c>
       <c r="K279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:01:04.392Z</t>
+          <t>2026-10-13T21:01:13.109Z</t>
         </is>
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:11Z</t>
+          <t>2026-10-13T23:47:50Z</t>
         </is>
       </c>
       <c r="M279" s="4" t="n"/>
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="D280" s="5" t="n">
-        <v>1007.664378</v>
+        <v>1010.0701</v>
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
@@ -18383,12 +18383,12 @@
       </c>
       <c r="K280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:01:04.382Z</t>
+          <t>2026-10-13T21:01:13.040Z</t>
         </is>
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:11Z</t>
+          <t>2026-10-13T23:47:50Z</t>
         </is>
       </c>
       <c r="M280" s="4" t="n"/>
@@ -18415,7 +18415,7 @@
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>1012.4591</v>
+        <v>1008.44</v>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
       <c r="K281" s="4" t="n"/>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:11Z</t>
+          <t>2026-10-13T23:47:50Z</t>
         </is>
       </c>
       <c r="M281" s="6" t="n">
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="D282" s="5" t="n">
-        <v>1012.035</v>
+        <v>1008.9436</v>
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
       <c r="K282" s="4" t="n"/>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:11Z</t>
+          <t>2026-10-13T23:47:50Z</t>
         </is>
       </c>
       <c r="M282" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N282"/>
+  <dimension ref="A1:N286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18526,6 +18526,266 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="n">
+        <v>1125.469688</v>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T21:01:08.350Z</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:44Z</t>
+        </is>
+      </c>
+      <c r="M283" s="4" t="n"/>
+      <c r="N283" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="n">
+        <v>1009.697123</v>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G284" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I284" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T21:01:08.292Z</t>
+        </is>
+      </c>
+      <c r="L284" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:44Z</t>
+        </is>
+      </c>
+      <c r="M284" s="4" t="n"/>
+      <c r="N284" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="n">
+        <v>1011.775</v>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H285" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I285" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K285" s="4" t="n"/>
+      <c r="L285" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:44Z</t>
+        </is>
+      </c>
+      <c r="M285" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N285" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="n">
+        <v>1012.7123</v>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G286" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K286" s="4" t="n"/>
+      <c r="L286" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:20:44Z</t>
+        </is>
+      </c>
+      <c r="M286" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N286" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N286"/>
+  <dimension ref="A1:N290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18786,6 +18786,266 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="n">
+        <v>1126.845014</v>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H287" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I287" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T21:01:05.749Z</t>
+        </is>
+      </c>
+      <c r="L287" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:32Z</t>
+        </is>
+      </c>
+      <c r="M287" s="4" t="n"/>
+      <c r="N287" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="n">
+        <v>1005.108567</v>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I288" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J288" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T21:01:05.735Z</t>
+        </is>
+      </c>
+      <c r="L288" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:32Z</t>
+        </is>
+      </c>
+      <c r="M288" s="4" t="n"/>
+      <c r="N288" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="n">
+        <v>1002.233</v>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H289" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I289" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K289" s="4" t="n"/>
+      <c r="L289" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:32Z</t>
+        </is>
+      </c>
+      <c r="M289" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N289" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="n">
+        <v>1002.2062</v>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I290" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J290" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K290" s="4" t="n"/>
+      <c r="L290" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:09:32Z</t>
+        </is>
+      </c>
+      <c r="M290" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N290" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N290"/>
+  <dimension ref="A1:N294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19046,6 +19046,266 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="n">
+        <v>1120.028606</v>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G291" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H291" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T21:01:09.925Z</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:15Z</t>
+        </is>
+      </c>
+      <c r="M291" s="4" t="n"/>
+      <c r="N291" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="n">
+        <v>997.480676</v>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T21:01:09.914Z</t>
+        </is>
+      </c>
+      <c r="L292" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:15Z</t>
+        </is>
+      </c>
+      <c r="M292" s="4" t="n"/>
+      <c r="N292" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="n">
+        <v>1002.2515</v>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G293" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H293" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I293" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K293" s="4" t="n"/>
+      <c r="L293" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:15Z</t>
+        </is>
+      </c>
+      <c r="M293" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N293" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="n">
+        <v>999.5281</v>
+      </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G294" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J294" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K294" s="4" t="n"/>
+      <c r="L294" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T22:56:15Z</t>
+        </is>
+      </c>
+      <c r="M294" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N294" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N294"/>
+  <dimension ref="A1:N298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19306,6 +19306,266 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="n">
+        <v>1127.087849</v>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G295" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H295" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I295" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K295" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17T21:01:00.987Z</t>
+        </is>
+      </c>
+      <c r="L295" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17T22:30:03Z</t>
+        </is>
+      </c>
+      <c r="M295" s="4" t="n"/>
+      <c r="N295" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="n">
+        <v>1004.027889</v>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I296" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K296" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17T21:01:00.973Z</t>
+        </is>
+      </c>
+      <c r="L296" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17T22:30:03Z</t>
+        </is>
+      </c>
+      <c r="M296" s="4" t="n"/>
+      <c r="N296" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="n">
+        <v>1003.9926</v>
+      </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H297" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K297" s="4" t="n"/>
+      <c r="L297" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17T22:30:03Z</t>
+        </is>
+      </c>
+      <c r="M297" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N297" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="n">
+        <v>1000.454</v>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H298" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="n"/>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17T22:30:03Z</t>
+        </is>
+      </c>
+      <c r="M298" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N298" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N298"/>
+  <dimension ref="A1:N302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19566,6 +19566,266 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="n">
+        <v>1122.922815</v>
+      </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H299" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I299" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K299" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:01:11.385Z</t>
+        </is>
+      </c>
+      <c r="L299" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18T22:31:05Z</t>
+        </is>
+      </c>
+      <c r="M299" s="4" t="n"/>
+      <c r="N299" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="n">
+        <v>1002.304061</v>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I300" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18T21:01:11.311Z</t>
+        </is>
+      </c>
+      <c r="L300" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18T22:31:05Z</t>
+        </is>
+      </c>
+      <c r="M300" s="4" t="n"/>
+      <c r="N300" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="n">
+        <v>1004.6502</v>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K301" s="4" t="n"/>
+      <c r="L301" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18T22:31:05Z</t>
+        </is>
+      </c>
+      <c r="M301" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N301" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="n">
+        <v>1003.7197</v>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I302" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K302" s="4" t="n"/>
+      <c r="L302" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18T22:31:05Z</t>
+        </is>
+      </c>
+      <c r="M302" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N302" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N302"/>
+  <dimension ref="A1:N306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19826,6 +19826,266 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="n">
+        <v>1127.683712</v>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G303" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H303" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I303" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T21:01:24.823Z</t>
+        </is>
+      </c>
+      <c r="L303" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:27Z</t>
+        </is>
+      </c>
+      <c r="M303" s="4" t="n"/>
+      <c r="N303" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="n">
+        <v>1007.134323</v>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K304" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T21:01:24.747Z</t>
+        </is>
+      </c>
+      <c r="L304" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:27Z</t>
+        </is>
+      </c>
+      <c r="M304" s="4" t="n"/>
+      <c r="N304" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="n">
+        <v>1005.381</v>
+      </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G305" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H305" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I305" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K305" s="4" t="n"/>
+      <c r="L305" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:27Z</t>
+        </is>
+      </c>
+      <c r="M305" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N305" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="n">
+        <v>982.2338999999999</v>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I306" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K306" s="4" t="n"/>
+      <c r="L306" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:50:27Z</t>
+        </is>
+      </c>
+      <c r="M306" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N306" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N306"/>
+  <dimension ref="A1:N310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -20086,6 +20086,266 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="n">
+        <v>1129.41109</v>
+      </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H307" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I307" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K307" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T21:01:02.279Z</t>
+        </is>
+      </c>
+      <c r="L307" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:44Z</t>
+        </is>
+      </c>
+      <c r="M307" s="4" t="n"/>
+      <c r="N307" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="n">
+        <v>1006.204764</v>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H308" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I308" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J308" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K308" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T21:01:02.268Z</t>
+        </is>
+      </c>
+      <c r="L308" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:44Z</t>
+        </is>
+      </c>
+      <c r="M308" s="4" t="n"/>
+      <c r="N308" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="n">
+        <v>1007.8551</v>
+      </c>
+      <c r="E309" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G309" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H309" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I309" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J309" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K309" s="4" t="n"/>
+      <c r="L309" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:44Z</t>
+        </is>
+      </c>
+      <c r="M309" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N309" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="n">
+        <v>1005.7157</v>
+      </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H310" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J310" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K310" s="4" t="n"/>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T23:16:44Z</t>
+        </is>
+      </c>
+      <c r="M310" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N310" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N310"/>
+  <dimension ref="A1:N314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -20346,6 +20346,266 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="n">
+        <v>1129.82665</v>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G311" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H311" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I311" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J311" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K311" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T21:01:12.634Z</t>
+        </is>
+      </c>
+      <c r="L311" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:30:01Z</t>
+        </is>
+      </c>
+      <c r="M311" s="4" t="n"/>
+      <c r="N311" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="n">
+        <v>1005.973923</v>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G312" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H312" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I312" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T21:01:12.595Z</t>
+        </is>
+      </c>
+      <c r="L312" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:30:01Z</t>
+        </is>
+      </c>
+      <c r="M312" s="4" t="n"/>
+      <c r="N312" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="n">
+        <v>1005.2331</v>
+      </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H313" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I313" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J313" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K313" s="4" t="n"/>
+      <c r="L313" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:30:01Z</t>
+        </is>
+      </c>
+      <c r="M313" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N313" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="n">
+        <v>1001.8045</v>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H314" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I314" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J314" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K314" s="4" t="n"/>
+      <c r="L314" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T23:30:01Z</t>
+        </is>
+      </c>
+      <c r="M314" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N314" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N314"/>
+  <dimension ref="A1:N318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -20606,6 +20606,266 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="n">
+        <v>1125.287244</v>
+      </c>
+      <c r="E315" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G315" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H315" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I315" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J315" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K315" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:01:17.155Z</t>
+        </is>
+      </c>
+      <c r="L315" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:17Z</t>
+        </is>
+      </c>
+      <c r="M315" s="4" t="n"/>
+      <c r="N315" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="n">
+        <v>1004.585558</v>
+      </c>
+      <c r="E316" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H316" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I316" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J316" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K316" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:01:17.116Z</t>
+        </is>
+      </c>
+      <c r="L316" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:17Z</t>
+        </is>
+      </c>
+      <c r="M316" s="4" t="n"/>
+      <c r="N316" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="n">
+        <v>1004.5876</v>
+      </c>
+      <c r="E317" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G317" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H317" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J317" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K317" s="4" t="n"/>
+      <c r="L317" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:17Z</t>
+        </is>
+      </c>
+      <c r="M317" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N317" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="n">
+        <v>1002.564</v>
+      </c>
+      <c r="E318" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G318" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H318" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I318" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J318" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K318" s="4" t="n"/>
+      <c r="L318" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T23:29:17Z</t>
+        </is>
+      </c>
+      <c r="M318" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N318" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N318"/>
+  <dimension ref="A1:N322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -20866,6 +20866,266 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="n">
+        <v>1119.610887</v>
+      </c>
+      <c r="E319" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G319" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H319" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I319" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J319" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K319" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:01:04.268Z</t>
+        </is>
+      </c>
+      <c r="L319" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:18:01Z</t>
+        </is>
+      </c>
+      <c r="M319" s="4" t="n"/>
+      <c r="N319" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="n">
+        <v>999.784532</v>
+      </c>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G320" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H320" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I320" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J320" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K320" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:01:04.230Z</t>
+        </is>
+      </c>
+      <c r="L320" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:18:01Z</t>
+        </is>
+      </c>
+      <c r="M320" s="4" t="n"/>
+      <c r="N320" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="n">
+        <v>1004.5581</v>
+      </c>
+      <c r="E321" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H321" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I321" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J321" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K321" s="4" t="n"/>
+      <c r="L321" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:18:01Z</t>
+        </is>
+      </c>
+      <c r="M321" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N321" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="n">
+        <v>1001.005</v>
+      </c>
+      <c r="E322" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H322" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I322" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J322" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K322" s="4" t="n"/>
+      <c r="L322" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:18:01Z</t>
+        </is>
+      </c>
+      <c r="M322" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N322" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N322"/>
+  <dimension ref="A1:N326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21126,6 +21126,266 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="n">
+        <v>1124.807909</v>
+      </c>
+      <c r="E323" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H323" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I323" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J323" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K323" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:01:07.488Z</t>
+        </is>
+      </c>
+      <c r="L323" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:37:10Z</t>
+        </is>
+      </c>
+      <c r="M323" s="4" t="n"/>
+      <c r="N323" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="n">
+        <v>1005.34881</v>
+      </c>
+      <c r="E324" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G324" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H324" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I324" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J324" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K324" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:01:07.428Z</t>
+        </is>
+      </c>
+      <c r="L324" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:37:10Z</t>
+        </is>
+      </c>
+      <c r="M324" s="4" t="n"/>
+      <c r="N324" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="n">
+        <v>1007.267</v>
+      </c>
+      <c r="E325" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H325" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I325" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K325" s="4" t="n"/>
+      <c r="L325" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:37:10Z</t>
+        </is>
+      </c>
+      <c r="M325" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N325" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="n">
+        <v>1003.8528</v>
+      </c>
+      <c r="E326" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F326" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G326" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H326" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I326" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J326" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K326" s="4" t="n"/>
+      <c r="L326" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:37:10Z</t>
+        </is>
+      </c>
+      <c r="M326" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N326" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N326"/>
+  <dimension ref="A1:N330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21386,6 +21386,266 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="n">
+        <v>1123.468698</v>
+      </c>
+      <c r="E327" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H327" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I327" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K327" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T21:01:04.320Z</t>
+        </is>
+      </c>
+      <c r="L327" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T22:43:44Z</t>
+        </is>
+      </c>
+      <c r="M327" s="4" t="n"/>
+      <c r="N327" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="n">
+        <v>1002.94747</v>
+      </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H328" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I328" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J328" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K328" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T21:01:04.283Z</t>
+        </is>
+      </c>
+      <c r="L328" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T22:43:44Z</t>
+        </is>
+      </c>
+      <c r="M328" s="4" t="n"/>
+      <c r="N328" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="n">
+        <v>1008.2491</v>
+      </c>
+      <c r="E329" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G329" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H329" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I329" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J329" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K329" s="4" t="n"/>
+      <c r="L329" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T22:43:44Z</t>
+        </is>
+      </c>
+      <c r="M329" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N329" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D330" s="5" t="n">
+        <v>1003.2509</v>
+      </c>
+      <c r="E330" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H330" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I330" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K330" s="4" t="n"/>
+      <c r="L330" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T22:43:44Z</t>
+        </is>
+      </c>
+      <c r="M330" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N330" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N330"/>
+  <dimension ref="A1:N334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21646,6 +21646,266 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D331" s="5" t="n">
+        <v>1120.463419</v>
+      </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G331" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H331" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J331" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T21:01:05.229Z</t>
+        </is>
+      </c>
+      <c r="L331" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T23:58:36Z</t>
+        </is>
+      </c>
+      <c r="M331" s="4" t="n"/>
+      <c r="N331" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="n">
+        <v>1003.61365</v>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H332" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J332" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K332" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T21:01:05.196Z</t>
+        </is>
+      </c>
+      <c r="L332" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T23:58:36Z</t>
+        </is>
+      </c>
+      <c r="M332" s="4" t="n"/>
+      <c r="N332" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D333" s="5" t="n">
+        <v>1001.1031</v>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H333" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="n"/>
+      <c r="L333" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T23:58:36Z</t>
+        </is>
+      </c>
+      <c r="M333" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N333" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="n">
+        <v>999.6365000000001</v>
+      </c>
+      <c r="E334" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H334" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I334" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J334" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K334" s="4" t="n"/>
+      <c r="L334" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T23:58:36Z</t>
+        </is>
+      </c>
+      <c r="M334" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N334" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N334"/>
+  <dimension ref="A1:N338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21906,6 +21906,266 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="n">
+        <v>1113.365632</v>
+      </c>
+      <c r="E335" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G335" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H335" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J335" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:01:11.229Z</t>
+        </is>
+      </c>
+      <c r="L335" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:35Z</t>
+        </is>
+      </c>
+      <c r="M335" s="4" t="n"/>
+      <c r="N335" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D336" s="5" t="n">
+        <v>1001.324308</v>
+      </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H336" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I336" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J336" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K336" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:01:11.161Z</t>
+        </is>
+      </c>
+      <c r="L336" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:35Z</t>
+        </is>
+      </c>
+      <c r="M336" s="4" t="n"/>
+      <c r="N336" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D337" s="5" t="n">
+        <v>1005.4416</v>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="n"/>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:35Z</t>
+        </is>
+      </c>
+      <c r="M337" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N337" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D338" s="5" t="n">
+        <v>1003.095</v>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G338" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H338" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I338" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J338" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K338" s="4" t="n"/>
+      <c r="L338" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27T23:53:35Z</t>
+        </is>
+      </c>
+      <c r="M338" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N338" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N338"/>
+  <dimension ref="A1:N342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22166,6 +22166,266 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="n">
+        <v>1116.828881</v>
+      </c>
+      <c r="E339" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H339" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I339" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J339" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K339" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T21:01:05.685Z</t>
+        </is>
+      </c>
+      <c r="L339" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:39Z</t>
+        </is>
+      </c>
+      <c r="M339" s="4" t="n"/>
+      <c r="N339" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D340" s="5" t="n">
+        <v>1004.02693</v>
+      </c>
+      <c r="E340" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H340" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J340" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T21:01:05.626Z</t>
+        </is>
+      </c>
+      <c r="L340" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:39Z</t>
+        </is>
+      </c>
+      <c r="M340" s="4" t="n"/>
+      <c r="N340" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="n">
+        <v>1007.41</v>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H341" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J341" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K341" s="4" t="n"/>
+      <c r="L341" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:39Z</t>
+        </is>
+      </c>
+      <c r="M341" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N341" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D342" s="5" t="n">
+        <v>1004.8738</v>
+      </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H342" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I342" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J342" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K342" s="4" t="n"/>
+      <c r="L342" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:09:39Z</t>
+        </is>
+      </c>
+      <c r="M342" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N342" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N342"/>
+  <dimension ref="A1:N346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22426,6 +22426,266 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="n">
+        <v>1116.47424</v>
+      </c>
+      <c r="E343" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G343" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H343" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J343" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T21:01:50.088Z</t>
+        </is>
+      </c>
+      <c r="L343" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:22Z</t>
+        </is>
+      </c>
+      <c r="M343" s="4" t="n"/>
+      <c r="N343" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="n">
+        <v>1002.21315</v>
+      </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H344" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I344" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J344" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T21:01:50.014Z</t>
+        </is>
+      </c>
+      <c r="L344" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:22Z</t>
+        </is>
+      </c>
+      <c r="M344" s="4" t="n"/>
+      <c r="N344" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="n">
+        <v>1002.738</v>
+      </c>
+      <c r="E345" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H345" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J345" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K345" s="4" t="n"/>
+      <c r="L345" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:22Z</t>
+        </is>
+      </c>
+      <c r="M345" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N345" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D346" s="5" t="n">
+        <v>998.9094</v>
+      </c>
+      <c r="E346" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H346" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I346" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J346" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K346" s="4" t="n"/>
+      <c r="L346" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:03:22Z</t>
+        </is>
+      </c>
+      <c r="M346" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N346" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -22443,7 +22443,7 @@
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>1116.47424</v>
+        <v>1107.964848</v>
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
@@ -22477,12 +22477,12 @@
       </c>
       <c r="K343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T21:01:50.088Z</t>
+          <t>2026-10-30T21:01:26.423Z</t>
         </is>
       </c>
       <c r="L343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:22Z</t>
+          <t>2026-10-30T23:56:09Z</t>
         </is>
       </c>
       <c r="M343" s="4" t="n"/>
@@ -22509,7 +22509,7 @@
         </is>
       </c>
       <c r="D344" s="5" t="n">
-        <v>1002.21315</v>
+        <v>993.118752</v>
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
@@ -22543,12 +22543,12 @@
       </c>
       <c r="K344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T21:01:50.014Z</t>
+          <t>2026-10-30T21:01:26.350Z</t>
         </is>
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:22Z</t>
+          <t>2026-10-30T23:56:09Z</t>
         </is>
       </c>
       <c r="M344" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>1002.738</v>
+        <v>986.1732</v>
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
       <c r="K345" s="4" t="n"/>
       <c r="L345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:22Z</t>
+          <t>2026-10-30T23:56:09Z</t>
         </is>
       </c>
       <c r="M345" s="6" t="n">
@@ -22639,7 +22639,7 @@
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>998.9094</v>
+        <v>980.0624</v>
       </c>
       <c r="E346" s="4" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
       <c r="K346" s="4" t="n"/>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:22Z</t>
+          <t>2026-10-30T23:56:09Z</t>
         </is>
       </c>
       <c r="M346" s="6" t="n">
